--- a/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="job_monitoring_policy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="file_channel_config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="file_template_config" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="pipeline_definition" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="pipeline_step_definition" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="workflow_definition" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="workflow_node" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="workflow_edge" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,72 +521,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>workflow_version</t>
+          <t>workflow_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>node_code</t>
+          <t>workflow_type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>node_name</t>
+          <t>version</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>node_type</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>related_job_code</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>related_pipeline_code</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>worker_group</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>window_code</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>node_order</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>retry_policy</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>retry_max_count</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>timeout_seconds</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>node_params</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>enabled</t>
+          <t>description</t>
         </is>
       </c>
     </row>
@@ -600,46 +556,27 @@
           <t>wf_probe_pipeline</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Probe PIPELINE workflow</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PIPELINE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>{"entry": true}</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>P2 seed - PIPELINE type</t>
         </is>
       </c>
     </row>
@@ -651,54 +588,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>wf_probe_pipeline</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+          <t>wf_probe_gateway</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Probe GATEWAY + ANY join</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DAG</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PROBE_TASK</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Probe Task</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TASK</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>exp_settlement_daily</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>{"step": "probe"}</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>P2 seed - GATEWAY + ANY join</t>
         </is>
       </c>
     </row>
@@ -710,609 +623,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>wf_probe_pipeline</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>wf_probe_mixed</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Probe MIXED workflow</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MIXED</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>{"entry": false}</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>wf_probe_gateway</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>{"entry": true}</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>wf_probe_gateway</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FORK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fork Gateway</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GATEWAY</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>wf_probe_gateway</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>BRANCH_A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Branch A</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>exp_settlement_daily</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>{"step": "branchA"}</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>wf_probe_gateway</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BRANCH_B</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Branch B</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>exp_settlement_daily</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>{"step": "branchB"}</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>wf_probe_gateway</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Merge Gateway</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>GATEWAY</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>{"joinMode": "ANY"}</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>wf_probe_gateway</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>{"entry": false}</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>wf_probe_mixed</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>START</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>{"entry": true}</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>wf_probe_mixed</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PROCESS</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Process Task</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>TASK</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>exp_settlement_daily</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>{"step": "process"}</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>wf_probe_mixed</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>REPORT</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generate Report</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>FILE_STEP</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>exp_settlement_daily</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>{"step": "report"}</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>wf_probe_mixed</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>END</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>{"entry": false}</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>P2 seed - MIXED type (TASK + FILE_STEP mixed)</t>
         </is>
       </c>
     </row>
@@ -1322,6 +656,829 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>tenant_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>workflow_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>workflow_version</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>node_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>node_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>node_type</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>related_job_code</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>related_pipeline_code</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>worker_group</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>window_code</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>node_order</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>retry_policy</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>retry_max_count</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>timeout_seconds</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>node_params</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>wf_probe_pipeline</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{"entry": true}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>wf_probe_pipeline</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PROBE_TASK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Probe Task</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>exp_settlement_daily</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>{"step": "probe"}</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>wf_probe_pipeline</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{"entry": false}</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{"entry": true}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FORK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fork Gateway</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BRANCH_A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Branch A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>exp_settlement_daily</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{"step": "branchA"}</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BRANCH_B</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Branch B</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>exp_settlement_daily</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>{"step": "branchB"}</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Merge Gateway</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>GATEWAY</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>{"joinMode": "ANY"}</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>wf_probe_gateway</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>{"entry": false}</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>wf_probe_mixed</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>{"entry": true}</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>wf_probe_mixed</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Process Task</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TASK</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>exp_settlement_daily</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>{"step": "process"}</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>wf_probe_mixed</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>REPORT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generate Report</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>FILE_STEP</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>exp_settlement_daily</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{"step": "report"}</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>wf_probe_mixed</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{"entry": false}</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2285,7 +2442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2296,247 +2453,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>channel_code</t>
+          <t>job_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>channel_name</t>
+          <t>soft_runtime_seconds</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>channel_type</t>
+          <t>soft_runtime_severity</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>target_endpoint</t>
+          <t>start_grace_seconds</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>auth_type</t>
+          <t>start_grace_severity</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>config_json</t>
+          <t>completion_deadline_local_time</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>receipt_policy</t>
+          <t>completion_deadline_day_offset</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>timeout_seconds</t>
+          <t>completion_grace_seconds</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>enabled</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>sftp_bank</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SFTP Bank Dispatch</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SFTP</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>localhost:12222</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{"target_endpoint": "localhost:12222", "sftp_host": "localhost", "sftp_port": 12222, "sftp_user": "ta", "sftp_password": "ta_pass_123", "sftp_remote_directory": "/inbound", "sftp_strict_host_key_checking": "no"}</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>email_ops</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Email Ops Dispatch</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>localhost:1025</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>{"target_endpoint": "localhost:1025", "smtp_host": "localhost", "smtp_port": 1025, "smtp_starttls": false, "mail_from": "batch@local.dev", "mail_to": "ops@local.dev", "mail_subject": "Batch Dispatch Probe"}</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nas_archive</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NAS Archive Dispatch</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NAS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>/tmp/batch/nas-probe</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>{"target_endpoint": "/tmp/batch/nas-probe", "nas_remote_directory": "/tmp/batch/nas-probe", "nas_remote_file_name": "settlement-{bizDate}.csv"}</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>30</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>oss_backup</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OSS Backup Dispatch</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OSS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>http://localhost:19000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>{"target_endpoint": "http://localhost:19000", "oss_bucket": "batch-dev", "oss_object_prefix": "dispatch/oss-probe/"}</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>completion_deadline_severity</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO1"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2562,202 +2519,247 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>template_code</t>
+          <t>channel_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>template_name</t>
+          <t>channel_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>template_type</t>
+          <t>channel_type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>biz_type</t>
+          <t>target_endpoint</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>file_format_type</t>
+          <t>auth_type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>charset</t>
+          <t>config_json</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>target_charset</t>
+          <t>receipt_policy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>with_bom</t>
+          <t>timeout_seconds</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>line_separator</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>delimiter</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>quote_char</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>escape_char</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>record_length</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>header_rows</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>footer_rows</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>header_template</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>trailer_template</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>checksum_type</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>compress_type</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>encrypt_type</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>naming_rule</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>field_mappings</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>validation_rule_set</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>default_query_code</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>default_query_sql</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>query_param_schema</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>streaming_enabled</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>page_size</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>fetch_size</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>chunk_size</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>preview_masking_enabled</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>error_line_masking_enabled</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>log_masking_enabled</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>content_encryption_enabled</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>encryption_key_ref</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>download_requires_approval</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>masking_rule_set</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>description</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sftp_bank</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SFTP Bank Dispatch</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SFTP</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>localhost:12222</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"target_endpoint": "localhost:12222", "sftp_host": "localhost", "sftp_port": 12222, "sftp_user": "ta", "sftp_password": "ta_pass_123", "sftp_remote_directory": "/inbound", "sftp_strict_host_key_checking": "no"}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>email_ops</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Email Ops Dispatch</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>localhost:1025</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>{"target_endpoint": "localhost:1025", "smtp_host": "localhost", "smtp_port": 1025, "smtp_starttls": false, "mail_from": "batch@local.dev", "mail_to": "ops@local.dev", "mail_subject": "Batch Dispatch Probe"}</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>30</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>nas_archive</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NAS Archive Dispatch</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NAS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>/tmp/batch/nas-probe</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{"target_endpoint": "/tmp/batch/nas-probe", "nas_remote_directory": "/tmp/batch/nas-probe", "nas_remote_file_name": "settlement-{bizDate}.csv"}</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>default-tenant</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>oss_backup</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OSS Backup Dispatch</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OSS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>http://localhost:19000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{"target_endpoint": "http://localhost:19000", "oss_bucket": "batch-dev", "oss_object_prefix": "dispatch/oss-probe/"}</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2783,17 +2785,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>job_code</t>
+          <t>template_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>pipeline_name</t>
+          <t>template_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>pipeline_type</t>
+          <t>template_type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -2803,20 +2805,180 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>worker_group</t>
+          <t>file_format_type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>charset</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>target_charset</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>with_bom</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>line_separator</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>delimiter</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>quote_char</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>escape_char</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>record_length</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>header_rows</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>footer_rows</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>header_template</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>trailer_template</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>checksum_type</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>compress_type</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>encrypt_type</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>naming_rule</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>field_mappings</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>validation_rule_set</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>default_query_code</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>default_query_sql</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>query_param_schema</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>streaming_enabled</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>page_size</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>fetch_size</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>chunk_size</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>preview_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>error_line_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>log_masking_enabled</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>content_encryption_enabled</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>encryption_key_ref</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>download_requires_approval</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>masking_rule_set</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
           <t>version</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2833,68 +2995,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>tenant_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>job_code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pipeline_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pipeline_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>biz_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>worker_group</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>step_code</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>step_name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>stage_code</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>step_order</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>impl_code</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>step_params</t>
+          <t>enabled</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>timeout_seconds</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>retry_policy</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>retry_max_count</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>enabled</t>
+          <t>description</t>
         </is>
       </c>
     </row>
@@ -2909,148 +3056,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>tenant_id</t>
+          <t>job_code</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>workflow_code</t>
+          <t>version</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>workflow_name</t>
+          <t>step_code</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>workflow_type</t>
+          <t>step_name</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>stage_code</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>step_order</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>impl_code</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>step_params</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>timeout_seconds</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>retry_policy</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>retry_max_count</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>enabled</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>wf_probe_pipeline</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Probe PIPELINE workflow</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PIPELINE</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>P2 seed - PIPELINE type</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>wf_probe_gateway</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Probe GATEWAY + ANY join</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DAG</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>P2 seed - GATEWAY + ANY join</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>default-tenant</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>wf_probe_mixed</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Probe MIXED workflow</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MIXED</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>P2 seed - MIXED type (TASK + FILE_STEP mixed)</t>
         </is>
       </c>
     </row>

--- a/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
+++ b/docs/test-data/test-full-coverage-import-suite/default-tenant-config-package-test.xlsx
@@ -2488,7 +2488,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>completion_grace_seconds</t>
+          <t>dependency_completion_window_seconds</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
